--- a/assets/constructions/examples/ctd_ne1_countersink.xlsx
+++ b/assets/constructions/examples/ctd_ne1_countersink.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ6"/>
+  <dimension ref="A1:AO6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -609,11 +609,36 @@
           <t>hand</t>
         </is>
       </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2320-2711 h8 Р6М5 ГОСТ 12489-87</t>
+          <t>2320-2732 h8 Р6АМ5 ГОСТ 12489-87</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -624,26 +649,26 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PNK</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5.8</v>
+        <v>15</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>51.2</v>
+        <v>99</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Р6М5</t>
+          <t>Р6АМ5</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -662,7 +687,7 @@
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>5.8</v>
+        <v>15</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -670,17 +695,17 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>93</v>
+        <v>169</v>
       </c>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
-        <v>57</v>
+        <v>114</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
@@ -706,7 +731,7 @@
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>HA-5.8</t>
+          <t>HA-15</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -717,13 +742,24 @@
       <c r="AJ2" t="inlineStr">
         <is>
           <t>R</t>
+        </is>
+      </c>
+      <c r="AK2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>PMKS</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2323-2709 u8 Р18 ГОСТ 12489-87</t>
+          <t>2320-2736 u8 Р18 ГОСТ 12489-87</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -734,7 +770,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PNKS</t>
+          <t>PKNS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -743,11 +779,11 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>47</v>
+        <v>108</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
@@ -772,7 +808,7 @@
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -780,17 +816,17 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>86</v>
+        <v>184</v>
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>52</v>
+        <v>125</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
@@ -816,7 +852,7 @@
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>HA-5</t>
+          <t>HA-17</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -827,13 +863,24 @@
       <c r="AJ3" t="inlineStr">
         <is>
           <t>R</t>
+        </is>
+      </c>
+      <c r="AK3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2320-2729 u8 Р6АМ5 ГОСТ 12489-87</t>
+          <t>2323-2724 h8 Р6АМ5 ГОСТ 12489-87</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -849,15 +896,15 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SM</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>14</v>
+        <v>11.75</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>94</v>
+        <v>82.25</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
@@ -882,7 +929,7 @@
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>14</v>
+        <v>11.75</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -890,17 +937,17 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
@@ -920,13 +967,13 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>u8</t>
+          <t>h8</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>HA-14</t>
+          <t>HA-11.75</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -937,13 +984,24 @@
       <c r="AJ4" t="inlineStr">
         <is>
           <t>R</t>
+        </is>
+      </c>
+      <c r="AK4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>PMKS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2323-2726 h8 Р6АМ5 ГОСТ 12489-87</t>
+          <t>2323-2706 u8 Р18 ГОСТ 12489-87</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -954,26 +1012,26 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>PKNS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SM</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>12.75</v>
+        <v>4.3</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>88.25</v>
+        <v>42.7</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Р6АМ5</t>
+          <t>Р18</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -992,7 +1050,7 @@
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>12.75</v>
+        <v>4.3</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -1000,17 +1058,17 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>151</v>
+        <v>80</v>
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>101</v>
+        <v>47</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
@@ -1030,13 +1088,13 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>h8</t>
+          <t>u8</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>HA-12.75</t>
+          <t>HA-4.3</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1047,13 +1105,24 @@
       <c r="AJ5" t="inlineStr">
         <is>
           <t>R</t>
+        </is>
+      </c>
+      <c r="AK5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2323-2717 h8 Р6М5 ГОСТ 12489-87</t>
+          <t>2320-2707 h8 Р18 ГОСТ 12489-87</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1064,7 +1133,7 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PNK</t>
+          <t>PKNS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1073,17 +1142,17 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>8.800000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>72.2</v>
+        <v>42.5</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Р6М5</t>
+          <t>Р18</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -1102,7 +1171,7 @@
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>8.800000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1110,17 +1179,17 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="n">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
@@ -1146,7 +1215,7 @@
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>HA-8.8</t>
+          <t>HA-4.5</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -1157,6 +1226,17 @@
       <c r="AJ6" t="inlineStr">
         <is>
           <t>R</t>
+        </is>
+      </c>
+      <c r="AK6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
         </is>
       </c>
     </row>
